--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="192">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Quantité exposition</t>
+    <t>Logical model - FR LM Quantité exposition</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:27:00+00:00</t>
+    <t>2026-04-24T08:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,57 +250,214 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-quantite-exposition.identifiant</t>
+    <t>fr-lm-quantite-exposition.header</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Métadonnées de base</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+</t>
+  </si>
+  <si>
+    <t>Patient/subject information</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.subject</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Identifiant de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-quantite-exposition.code</t>
+    <t>Identifiant de l’entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.identifier</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.author[x]</t>
+  </si>
+  <si>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
+  </si>
+  <si>
+    <t>Exécutant (performer)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.participant[x]</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.informant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
+</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.informant</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date/Heure de création par l'auteur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.date</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.source</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.header.langue</t>
+  </si>
+  <si>
+    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
+La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
+La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.langue</t>
+  </si>
+  <si>
+    <t>fr-lm-quantite-exposition.code</t>
+  </si>
+  <si>
     <t>Code de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-quantite-exposition.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Partie narrative de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-quantite-exposition.statut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>status de l'observation</t>
-  </si>
-  <si>
-    <t>fr-lm-quantite-exposition.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de l'observation</t>
   </si>
   <si>
     <t>fr-lm-quantite-exposition.valeur</t>
@@ -754,11 +911,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.25" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.25" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.80859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.80859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -767,7 +924,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -782,13 +939,13 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="50.56640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.5" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1089,7 +1246,7 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
@@ -1106,10 +1263,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1132,13 +1289,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1189,7 +1346,7 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1206,10 +1363,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1220,7 +1377,7 @@
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1232,13 +1389,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1289,13 +1446,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1306,10 +1463,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1317,10 +1474,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1332,13 +1489,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1389,13 +1546,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1406,10 +1563,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1420,7 +1577,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1432,13 +1589,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1489,13 +1646,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1506,10 +1663,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1517,10 +1674,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1532,13 +1689,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1589,13 +1746,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1606,10 +1763,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1620,7 +1777,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1632,13 +1789,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1668,7 +1825,7 @@
         <v>73</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="Z9" t="s" s="2">
         <v>73</v>
@@ -1689,27 +1846,27 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1720,7 +1877,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1732,13 +1889,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1789,13 +1946,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1806,14 +1963,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -1832,17 +1989,15 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>111</v>
       </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -1879,19 +2034,19 @@
         <v>73</v>
       </c>
       <c r="AB11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1903,15 +2058,15 @@
         <v>73</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>116</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1931,23 +2086,19 @@
         <v>73</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
       </c>
@@ -1995,7 +2146,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2007,15 +2158,15 @@
         <v>73</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2026,7 +2177,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2035,23 +2186,19 @@
         <v>73</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>73</v>
       </c>
@@ -2099,27 +2246,27 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2130,7 +2277,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2142,13 +2289,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2199,27 +2346,27 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2230,7 +2377,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2242,13 +2389,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2299,13 +2446,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2316,21 +2463,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2342,17 +2489,15 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>73</v>
@@ -2389,39 +2534,39 @@
         <v>73</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>116</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2429,10 +2574,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2441,23 +2586,19 @@
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>123</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>73</v>
       </c>
@@ -2484,10 +2625,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2505,19 +2646,19 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -2545,23 +2686,19 @@
         <v>73</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
       </c>
@@ -2609,7 +2746,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2621,15 +2758,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2637,7 +2774,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2652,13 +2789,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2709,10 +2846,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2726,10 +2863,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2752,13 +2889,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2788,7 +2925,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2809,7 +2946,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2821,6 +2958,1326 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-quantite-exposition.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-quantite-exposition.header.langue</t>
+    <t>fr-lm-quantite-exposition.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-quantite-exposition.code</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="190">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,7 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -939,7 +933,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="50.56640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2574,7 +2568,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2625,31 +2619,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2663,10 +2657,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2692,10 +2686,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2746,7 +2740,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2763,10 +2757,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2792,10 +2786,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2846,7 +2840,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2863,10 +2857,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2892,10 +2886,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2946,7 +2940,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2963,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2989,13 +2983,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3046,7 +3040,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3063,10 +3057,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3092,10 +3086,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3125,7 +3119,7 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3146,7 +3140,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3158,15 +3152,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3189,13 +3183,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3246,7 +3240,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3263,14 +3257,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3289,16 +3283,16 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3336,19 +3330,19 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AC24" t="s" s="2">
+      <c r="AF24" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3360,15 +3354,15 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3388,22 +3382,22 @@
         <v>73</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -3452,7 +3446,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3464,15 +3458,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3492,22 +3486,22 @@
         <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>73</v>
@@ -3556,7 +3550,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3568,15 +3562,15 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3602,10 +3596,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3656,7 +3650,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3668,15 +3662,15 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3699,13 +3693,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3756,7 +3750,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3773,14 +3767,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -3799,16 +3793,16 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3846,19 +3840,19 @@
         <v>73</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3870,15 +3864,15 @@
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3898,22 +3892,22 @@
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="K30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>73</v>
@@ -3962,7 +3956,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3974,15 +3968,15 @@
         <v>73</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4002,22 +3996,22 @@
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>73</v>
@@ -4066,7 +4060,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4078,15 +4072,15 @@
         <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4112,10 +4106,10 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4166,7 +4160,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4183,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4212,10 +4206,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4245,7 +4239,7 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>73</v>
@@ -4266,7 +4260,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-quantite-exposition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
